--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/14.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/14.xlsx
@@ -426,13 +426,13 @@
         <v>-18.89216120216067</v>
       </c>
       <c r="E2">
-        <v>-20.03214611161617</v>
+        <v>-16.96429516732783</v>
       </c>
       <c r="F2">
-        <v>-1.337713270312971</v>
+        <v>-0.8948912510636332</v>
       </c>
       <c r="G2">
-        <v>-13.64339360568391</v>
+        <v>-8.217001264877904</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.69006169674415</v>
       </c>
       <c r="E3">
-        <v>-21.00217241490321</v>
+        <v>-18.03373053203124</v>
       </c>
       <c r="F3">
-        <v>-1.577726926702308</v>
+        <v>-1.341592514860281</v>
       </c>
       <c r="G3">
-        <v>-14.00379805994098</v>
+        <v>-7.661890763894167</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.47025352008566</v>
       </c>
       <c r="E4">
-        <v>-21.011496542885</v>
+        <v>-16.93796661944723</v>
       </c>
       <c r="F4">
-        <v>-1.4684495272924</v>
+        <v>-0.9071999623018311</v>
       </c>
       <c r="G4">
-        <v>-13.5059005786785</v>
+        <v>-7.402208327236593</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.25110108862367</v>
       </c>
       <c r="E5">
-        <v>-21.81948046075557</v>
+        <v>-17.51172427621907</v>
       </c>
       <c r="F5">
-        <v>-1.450320706682133</v>
+        <v>-1.05464853163274</v>
       </c>
       <c r="G5">
-        <v>-13.35877716639612</v>
+        <v>-8.723254376841512</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.03006261553543</v>
       </c>
       <c r="E6">
-        <v>-22.18144138818866</v>
+        <v>-18.38769417436679</v>
       </c>
       <c r="F6">
-        <v>-1.444405335058741</v>
+        <v>-1.021557738993109</v>
       </c>
       <c r="G6">
-        <v>-13.15269348391207</v>
+        <v>-7.827539953101174</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.80696051602552</v>
       </c>
       <c r="E7">
-        <v>-22.82799879310781</v>
+        <v>-18.54920219985035</v>
       </c>
       <c r="F7">
-        <v>-1.464779031330595</v>
+        <v>-1.131645281722954</v>
       </c>
       <c r="G7">
-        <v>-12.97848358765648</v>
+        <v>-7.337154828599042</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.58365955021857</v>
       </c>
       <c r="E8">
-        <v>-22.24850355976825</v>
+        <v>-20.26087027679559</v>
       </c>
       <c r="F8">
-        <v>-1.045017932207793</v>
+        <v>-0.352715673889926</v>
       </c>
       <c r="G8">
-        <v>-12.77149100680046</v>
+        <v>-7.127724300124364</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.34922859525029</v>
       </c>
       <c r="E9">
-        <v>-23.69974815348038</v>
+        <v>-20.26710145703014</v>
       </c>
       <c r="F9">
-        <v>-1.193025649535592</v>
+        <v>-0.8915620424717821</v>
       </c>
       <c r="G9">
-        <v>-12.68603159128473</v>
+        <v>-8.140919580579061</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-17.08906232869443</v>
       </c>
       <c r="E10">
-        <v>-24.30328052685265</v>
+        <v>-20.94017307726419</v>
       </c>
       <c r="F10">
-        <v>-0.7900920058332594</v>
+        <v>-0.6012697982021261</v>
       </c>
       <c r="G10">
-        <v>-12.54629420873265</v>
+        <v>-7.413981350191881</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.80289592221165</v>
       </c>
       <c r="E11">
-        <v>-24.71504108294809</v>
+        <v>-20.57500599023367</v>
       </c>
       <c r="F11">
-        <v>-0.9739067325144697</v>
+        <v>-0.6820919489584683</v>
       </c>
       <c r="G11">
-        <v>-12.29300359167288</v>
+        <v>-7.690959105689288</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.47855659446374</v>
       </c>
       <c r="E12">
-        <v>-24.91275425812298</v>
+        <v>-22.2895043634337</v>
       </c>
       <c r="F12">
-        <v>-0.7115611193130607</v>
+        <v>0.1280497142446426</v>
       </c>
       <c r="G12">
-        <v>-11.56881502495251</v>
+        <v>-7.52123463930545</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.10559941951504</v>
       </c>
       <c r="E13">
-        <v>-25.5757137958979</v>
+        <v>-22.17003416216334</v>
       </c>
       <c r="F13">
-        <v>-0.691199020184846</v>
+        <v>0.4455993879034163</v>
       </c>
       <c r="G13">
-        <v>-11.26725435753175</v>
+        <v>-7.756137290746097</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.69538933793482</v>
       </c>
       <c r="E14">
-        <v>-26.87161814572491</v>
+        <v>-22.89300956596192</v>
       </c>
       <c r="F14">
-        <v>-0.5351611092543087</v>
+        <v>0.7465104739095592</v>
       </c>
       <c r="G14">
-        <v>-10.3192339809123</v>
+        <v>-6.190692734507499</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.24613444655824</v>
       </c>
       <c r="E15">
-        <v>-27.22300055787609</v>
+        <v>-24.60066994341037</v>
       </c>
       <c r="F15">
-        <v>-0.2152613572737929</v>
+        <v>0.1150816225538164</v>
       </c>
       <c r="G15">
-        <v>-10.3382552222924</v>
+        <v>-6.570011790443987</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.75909429099598</v>
       </c>
       <c r="E16">
-        <v>-28.01590918577512</v>
+        <v>-24.78218929553383</v>
       </c>
       <c r="F16">
-        <v>-0.2822945042431345</v>
+        <v>1.404911796267857</v>
       </c>
       <c r="G16">
-        <v>-9.595216037713028</v>
+        <v>-6.927363068039991</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-14.25610682639734</v>
       </c>
       <c r="E17">
-        <v>-28.65074689996241</v>
+        <v>-25.33970784451415</v>
       </c>
       <c r="F17">
-        <v>0.05710998660369856</v>
+        <v>1.804077196654854</v>
       </c>
       <c r="G17">
-        <v>-9.432395261490262</v>
+        <v>-6.67162465969687</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-13.74486879722378</v>
       </c>
       <c r="E18">
-        <v>-29.22396113985333</v>
+        <v>-26.59464308999377</v>
       </c>
       <c r="F18">
-        <v>0.1752583725301864</v>
+        <v>1.481068581811632</v>
       </c>
       <c r="G18">
-        <v>-9.001725088148465</v>
+        <v>-5.630489777663502</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-13.23403754641398</v>
       </c>
       <c r="E19">
-        <v>-30.1024986827634</v>
+        <v>-27.01915582889481</v>
       </c>
       <c r="F19">
-        <v>0.2818452346158016</v>
+        <v>1.842054528603601</v>
       </c>
       <c r="G19">
-        <v>-8.427258661185563</v>
+        <v>-7.263530779248222</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-12.74789490393118</v>
       </c>
       <c r="E20">
-        <v>-30.58180595715725</v>
+        <v>-27.74817674549363</v>
       </c>
       <c r="F20">
-        <v>0.4245456019938641</v>
+        <v>2.554442211337147</v>
       </c>
       <c r="G20">
-        <v>-8.554258341643871</v>
+        <v>-5.34562724675875</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-12.29304169436496</v>
       </c>
       <c r="E21">
-        <v>-31.62013976237599</v>
+        <v>-28.41206462044013</v>
       </c>
       <c r="F21">
-        <v>0.8005945816383389</v>
+        <v>2.296616170685412</v>
       </c>
       <c r="G21">
-        <v>-8.035474244544744</v>
+        <v>-4.745245731919353</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.87389888467385</v>
       </c>
       <c r="E22">
-        <v>-32.17645147303327</v>
+        <v>-29.15579854908987</v>
       </c>
       <c r="F22">
-        <v>0.8324154870494791</v>
+        <v>2.668826495785314</v>
       </c>
       <c r="G22">
-        <v>-8.443251335066297</v>
+        <v>-4.94209605693512</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.50636731468449</v>
       </c>
       <c r="E23">
-        <v>-32.24944820979992</v>
+        <v>-29.48570240902266</v>
       </c>
       <c r="F23">
-        <v>0.7776703421332654</v>
+        <v>3.315975275343983</v>
       </c>
       <c r="G23">
-        <v>-7.853688007708389</v>
+        <v>-4.781942913840183</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.18878749318056</v>
       </c>
       <c r="E24">
-        <v>-32.9403099401731</v>
+        <v>-31.19566098703</v>
       </c>
       <c r="F24">
-        <v>1.059470992156823</v>
+        <v>3.170719394528284</v>
       </c>
       <c r="G24">
-        <v>-7.592174649420645</v>
+        <v>-4.153205082284065</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.91806715890385</v>
       </c>
       <c r="E25">
-        <v>-33.26971793220206</v>
+        <v>-29.52199812819414</v>
       </c>
       <c r="F25">
-        <v>1.320163184022245</v>
+        <v>3.157510247923244</v>
       </c>
       <c r="G25">
-        <v>-7.978912547303037</v>
+        <v>-4.648804067844154</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.70055322100884</v>
       </c>
       <c r="E26">
-        <v>-33.40982891799938</v>
+        <v>-30.84469519448754</v>
       </c>
       <c r="F26">
-        <v>1.259602899938379</v>
+        <v>3.444812914236196</v>
       </c>
       <c r="G26">
-        <v>-7.593168859553157</v>
+        <v>-4.89748456861291</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.52720124368804</v>
       </c>
       <c r="E27">
-        <v>-33.11449090016713</v>
+        <v>-31.02909692031687</v>
       </c>
       <c r="F27">
-        <v>1.329994248358669</v>
+        <v>3.100420823257107</v>
       </c>
       <c r="G27">
-        <v>-7.676679229462584</v>
+        <v>-4.196970015443939</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.38873367797119</v>
       </c>
       <c r="E28">
-        <v>-33.52354795727999</v>
+        <v>-30.49329013996632</v>
       </c>
       <c r="F28">
-        <v>1.299483820178758</v>
+        <v>3.614265406887669</v>
       </c>
       <c r="G28">
-        <v>-8.110797966663357</v>
+        <v>-4.305227358354698</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.2838763663264</v>
       </c>
       <c r="E29">
-        <v>-33.66916556747064</v>
+        <v>-31.29151066787635</v>
       </c>
       <c r="F29">
-        <v>1.154711705926294</v>
+        <v>3.426719713424249</v>
       </c>
       <c r="G29">
-        <v>-8.058862791820466</v>
+        <v>-4.237821223859025</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.19891877421621</v>
       </c>
       <c r="E30">
-        <v>-33.38899114485308</v>
+        <v>-30.48865298258247</v>
       </c>
       <c r="F30">
-        <v>1.122469989874532</v>
+        <v>3.175346654840322</v>
       </c>
       <c r="G30">
-        <v>-8.025834015603095</v>
+        <v>-5.432783053820721</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.12292884127875</v>
       </c>
       <c r="E31">
-        <v>-33.1135852053656</v>
+        <v>-31.25850714930845</v>
       </c>
       <c r="F31">
-        <v>1.017462824426055</v>
+        <v>3.022285896355446</v>
       </c>
       <c r="G31">
-        <v>-8.388576340221269</v>
+        <v>-4.927409309235045</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.053133663824</v>
       </c>
       <c r="E32">
-        <v>-32.53403110186395</v>
+        <v>-30.37216025297215</v>
       </c>
       <c r="F32">
-        <v>1.146249104539294</v>
+        <v>3.240583901280395</v>
       </c>
       <c r="G32">
-        <v>-8.051391450329611</v>
+        <v>-5.437343951788349</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.978384772904201</v>
       </c>
       <c r="E33">
-        <v>-32.86244509384822</v>
+        <v>-30.32422182712696</v>
       </c>
       <c r="F33">
-        <v>1.227379407969478</v>
+        <v>2.775130884586575</v>
       </c>
       <c r="G33">
-        <v>-8.625529755136569</v>
+        <v>-4.963824306101763</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.893712862104792</v>
       </c>
       <c r="E34">
-        <v>-32.74721354424904</v>
+        <v>-29.16804354280661</v>
       </c>
       <c r="F34">
-        <v>1.167859553343528</v>
+        <v>3.133858701838512</v>
       </c>
       <c r="G34">
-        <v>-8.316504308668065</v>
+        <v>-4.572578009796694</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.802659525935862</v>
       </c>
       <c r="E35">
-        <v>-32.43038112453938</v>
+        <v>-30.51849336205601</v>
       </c>
       <c r="F35">
-        <v>1.019778939684282</v>
+        <v>2.531257864467595</v>
       </c>
       <c r="G35">
-        <v>-8.559052206342219</v>
+        <v>-5.172621558815468</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.701989746769183</v>
       </c>
       <c r="E36">
-        <v>-32.3914249268884</v>
+        <v>-30.40275462336797</v>
       </c>
       <c r="F36">
-        <v>1.216242836606241</v>
+        <v>2.955774620849869</v>
       </c>
       <c r="G36">
-        <v>-8.804208675156131</v>
+        <v>-5.027224069073354</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.595638797542597</v>
       </c>
       <c r="E37">
-        <v>-31.56688717228279</v>
+        <v>-27.4877940185266</v>
       </c>
       <c r="F37">
-        <v>1.22585024174391</v>
+        <v>3.099698486881866</v>
       </c>
       <c r="G37">
-        <v>-8.659418211402514</v>
+        <v>-3.703156014412187</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.493831615207618</v>
       </c>
       <c r="E38">
-        <v>-31.28532703661888</v>
+        <v>-27.38438631456144</v>
       </c>
       <c r="F38">
-        <v>1.46489719337418</v>
+        <v>2.778136201523931</v>
       </c>
       <c r="G38">
-        <v>-8.372281793957066</v>
+        <v>-4.564735890269621</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.399122652125367</v>
       </c>
       <c r="E39">
-        <v>-31.1344926243714</v>
+        <v>-28.90322291131206</v>
       </c>
       <c r="F39">
-        <v>1.132140350934813</v>
+        <v>2.890832273205193</v>
       </c>
       <c r="G39">
-        <v>-8.669950932608332</v>
+        <v>-4.692480408021923</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.319726244688155</v>
       </c>
       <c r="E40">
-        <v>-30.86216378297213</v>
+        <v>-28.46828562524536</v>
       </c>
       <c r="F40">
-        <v>1.119257581086475</v>
+        <v>2.33310575477873</v>
       </c>
       <c r="G40">
-        <v>-9.009334240944817</v>
+        <v>-4.543972320241455</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.265316942640732</v>
       </c>
       <c r="E41">
-        <v>-30.09936724298709</v>
+        <v>-27.26919552122833</v>
       </c>
       <c r="F41">
-        <v>1.321375913899943</v>
+        <v>2.509142111547654</v>
       </c>
       <c r="G41">
-        <v>-8.501985200980357</v>
+        <v>-5.834552227666929</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.234737622474819</v>
       </c>
       <c r="E42">
-        <v>-29.75404845753219</v>
+        <v>-26.26260631880336</v>
       </c>
       <c r="F42">
-        <v>1.318604196570176</v>
+        <v>2.382701767919142</v>
       </c>
       <c r="G42">
-        <v>-9.003693821084132</v>
+        <v>-4.752877853266622</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.230038025344474</v>
       </c>
       <c r="E43">
-        <v>-29.17960020847419</v>
+        <v>-24.99700198856167</v>
       </c>
       <c r="F43">
-        <v>1.080675540933685</v>
+        <v>3.115212151601495</v>
       </c>
       <c r="G43">
-        <v>-8.531358696380506</v>
+        <v>-4.310877621880062</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.252140610463886</v>
       </c>
       <c r="E44">
-        <v>-28.6204514088511</v>
+        <v>-25.97450027396137</v>
       </c>
       <c r="F44">
-        <v>1.223800860789384</v>
+        <v>2.721608409956893</v>
       </c>
       <c r="G44">
-        <v>-8.653699042224401</v>
+        <v>-4.017352666058375</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.29310718013088</v>
       </c>
       <c r="E45">
-        <v>-28.04693828967568</v>
+        <v>-25.28735868498548</v>
       </c>
       <c r="F45">
-        <v>1.280828986267713</v>
+        <v>2.365900820255563</v>
       </c>
       <c r="G45">
-        <v>-8.861436460374406</v>
+        <v>-4.704168119216665</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.351125977685976</v>
       </c>
       <c r="E46">
-        <v>-27.61555132723099</v>
+        <v>-23.30057675512626</v>
       </c>
       <c r="F46">
-        <v>1.149256078211456</v>
+        <v>2.583499683092549</v>
       </c>
       <c r="G46">
-        <v>-8.753244741894836</v>
+        <v>-4.257423241455148</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.425636896776727</v>
       </c>
       <c r="E47">
-        <v>-27.49525241521723</v>
+        <v>-24.98605213841113</v>
       </c>
       <c r="F47">
-        <v>1.437247946203538</v>
+        <v>2.526672022525697</v>
       </c>
       <c r="G47">
-        <v>-9.09831112597228</v>
+        <v>-3.826293697095029</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.510447070069251</v>
       </c>
       <c r="E48">
-        <v>-26.89538810579117</v>
+        <v>-24.75402218720611</v>
       </c>
       <c r="F48">
-        <v>1.185086281852146</v>
+        <v>2.139885744606135</v>
       </c>
       <c r="G48">
-        <v>-9.040840530358606</v>
+        <v>-3.959931288768093</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.604392437229791</v>
       </c>
       <c r="E49">
-        <v>-25.60235933695903</v>
+        <v>-24.1060066136565</v>
       </c>
       <c r="F49">
-        <v>1.083253420291197</v>
+        <v>2.705100704353904</v>
       </c>
       <c r="G49">
-        <v>-8.816464037680657</v>
+        <v>-4.202114970849148</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.708431845188626</v>
       </c>
       <c r="E50">
-        <v>-25.60484546918925</v>
+        <v>-22.45521028432237</v>
       </c>
       <c r="F50">
-        <v>1.294043103077171</v>
+        <v>2.41885669158173</v>
       </c>
       <c r="G50">
-        <v>-8.596077510418993</v>
+        <v>-4.700460338854493</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.81969955549676</v>
       </c>
       <c r="E51">
-        <v>-25.52780254089675</v>
+        <v>-22.48838135642856</v>
       </c>
       <c r="F51">
-        <v>1.101755834600127</v>
+        <v>2.594387744234945</v>
       </c>
       <c r="G51">
-        <v>-9.578744305484616</v>
+        <v>-4.68558328030397</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.938833181259533</v>
       </c>
       <c r="E52">
-        <v>-24.73299195391449</v>
+        <v>-22.06251913227323</v>
       </c>
       <c r="F52">
-        <v>1.254041241195983</v>
+        <v>3.070067784883728</v>
       </c>
       <c r="G52">
-        <v>-9.05175059204376</v>
+        <v>-4.608641915956551</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-10.06759392556876</v>
       </c>
       <c r="E53">
-        <v>-24.26495605132573</v>
+        <v>-22.25013381041101</v>
       </c>
       <c r="F53">
-        <v>1.215604993706086</v>
+        <v>2.634532085309415</v>
       </c>
       <c r="G53">
-        <v>-9.286659805927526</v>
+        <v>-4.472730437742792</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-10.20464764662225</v>
       </c>
       <c r="E54">
-        <v>-23.81253885558942</v>
+        <v>-20.72957639353749</v>
       </c>
       <c r="F54">
-        <v>1.295573926037544</v>
+        <v>2.495117851418258</v>
       </c>
       <c r="G54">
-        <v>-9.746706755891031</v>
+        <v>-4.491449806739423</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-10.34882307261105</v>
       </c>
       <c r="E55">
-        <v>-24.01867046394457</v>
+        <v>-21.99754458721118</v>
       </c>
       <c r="F55">
-        <v>1.03320014834444</v>
+        <v>2.431992941855325</v>
       </c>
       <c r="G55">
-        <v>-9.791436368189382</v>
+        <v>-5.729441576231677</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-10.49934123857523</v>
       </c>
       <c r="E56">
-        <v>-23.19866344758364</v>
+        <v>-19.97122002231697</v>
       </c>
       <c r="F56">
-        <v>1.129945177317394</v>
+        <v>2.459665383313244</v>
       </c>
       <c r="G56">
-        <v>-9.648883697539306</v>
+        <v>-4.047014908955756</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.65388847220429</v>
       </c>
       <c r="E57">
-        <v>-23.22528181780072</v>
+        <v>-19.22807932376224</v>
       </c>
       <c r="F57">
-        <v>1.076843513328335</v>
+        <v>2.251770016232653</v>
       </c>
       <c r="G57">
-        <v>-10.18255469685363</v>
+        <v>-5.420740970697558</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.80824942668682</v>
       </c>
       <c r="E58">
-        <v>-22.05050509073088</v>
+        <v>-20.4929002280006</v>
       </c>
       <c r="F58">
-        <v>1.131628419879883</v>
+        <v>2.010584219968354</v>
       </c>
       <c r="G58">
-        <v>-9.982761116099043</v>
+        <v>-4.660783807757687</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.95912863261346</v>
       </c>
       <c r="E59">
-        <v>-21.8830828781933</v>
+        <v>-17.13256420450484</v>
       </c>
       <c r="F59">
-        <v>1.2216454488073</v>
+        <v>2.539657509931982</v>
       </c>
       <c r="G59">
-        <v>-9.857129705031024</v>
+        <v>-5.236552879679689</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.10416183648485</v>
       </c>
       <c r="E60">
-        <v>-21.75972724622436</v>
+        <v>-20.59106848753888</v>
       </c>
       <c r="F60">
-        <v>0.9910876063209187</v>
+        <v>2.252934700800989</v>
       </c>
       <c r="G60">
-        <v>-10.63871996171232</v>
+        <v>-5.39018295431445</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.23656741593413</v>
       </c>
       <c r="E61">
-        <v>-21.31564244266217</v>
+        <v>-18.73264162495306</v>
       </c>
       <c r="F61">
-        <v>0.9064665626553381</v>
+        <v>2.116880325095587</v>
       </c>
       <c r="G61">
-        <v>-10.13343481010875</v>
+        <v>-4.703200158856629</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.35061279959933</v>
       </c>
       <c r="E62">
-        <v>-20.60904652934933</v>
+        <v>-17.23143890598832</v>
       </c>
       <c r="F62">
-        <v>0.5974275356929265</v>
+        <v>1.877230321996079</v>
       </c>
       <c r="G62">
-        <v>-10.33609289728473</v>
+        <v>-5.36554426162458</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.44546943591312</v>
       </c>
       <c r="E63">
-        <v>-21.14260945082908</v>
+        <v>-18.09620535944106</v>
       </c>
       <c r="F63">
-        <v>0.6541044333924687</v>
+        <v>1.999099734295942</v>
       </c>
       <c r="G63">
-        <v>-10.44164979485207</v>
+        <v>-7.305057919304554</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.51425777227222</v>
       </c>
       <c r="E64">
-        <v>-20.27419304732615</v>
+        <v>-17.72900045910709</v>
       </c>
       <c r="F64">
-        <v>0.8466948843389369</v>
+        <v>2.003672322359395</v>
       </c>
       <c r="G64">
-        <v>-10.69441541646233</v>
+        <v>-6.727064179165248</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-11.55226946741878</v>
       </c>
       <c r="E65">
-        <v>-20.81712538152777</v>
+        <v>-16.59025227124227</v>
       </c>
       <c r="F65">
-        <v>0.7560946847599493</v>
+        <v>1.773749009303559</v>
       </c>
       <c r="G65">
-        <v>-10.76001359787875</v>
+        <v>-7.611002298728739</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-11.56217256532378</v>
       </c>
       <c r="E66">
-        <v>-20.29102538521266</v>
+        <v>-17.92759668671347</v>
       </c>
       <c r="F66">
-        <v>0.6620609022963579</v>
+        <v>1.809027520253984</v>
       </c>
       <c r="G66">
-        <v>-10.94135030736146</v>
+        <v>-6.941213104242408</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-11.5389227167957</v>
       </c>
       <c r="E67">
-        <v>-20.60152473402259</v>
+        <v>-18.40989275395239</v>
       </c>
       <c r="F67">
-        <v>0.5584785287806965</v>
+        <v>1.347143110331425</v>
       </c>
       <c r="G67">
-        <v>-10.90157205839631</v>
+        <v>-7.64325342543652</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-11.48047182136672</v>
       </c>
       <c r="E68">
-        <v>-19.96363029988012</v>
+        <v>-15.44678088498745</v>
       </c>
       <c r="F68">
-        <v>0.2429807211786572</v>
+        <v>1.568184668094445</v>
       </c>
       <c r="G68">
-        <v>-11.03933742679116</v>
+        <v>-6.482839577274219</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-11.39292153240991</v>
       </c>
       <c r="E69">
-        <v>-19.23641624441036</v>
+        <v>-17.52386964350764</v>
       </c>
       <c r="F69">
-        <v>0.1027256943736589</v>
+        <v>1.688975546035863</v>
       </c>
       <c r="G69">
-        <v>-11.18333711614895</v>
+        <v>-7.048469674577537</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-11.27362310888687</v>
       </c>
       <c r="E70">
-        <v>-18.9637975806746</v>
+        <v>-15.87840332808054</v>
       </c>
       <c r="F70">
-        <v>0.2701097536203411</v>
+        <v>1.059550515427492</v>
       </c>
       <c r="G70">
-        <v>-10.76169358331718</v>
+        <v>-7.490082721820082</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-11.12282402719081</v>
       </c>
       <c r="E71">
-        <v>-19.70988178733432</v>
+        <v>-16.50817367985325</v>
       </c>
       <c r="F71">
-        <v>0.2080087061672677</v>
+        <v>1.39785576273081</v>
       </c>
       <c r="G71">
-        <v>-11.06873717196378</v>
+        <v>-7.141859802602452</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.94936980635921</v>
       </c>
       <c r="E72">
-        <v>-19.15451426350763</v>
+        <v>-15.25232368262408</v>
       </c>
       <c r="F72">
-        <v>0.0862179887706704</v>
+        <v>1.551304197160196</v>
       </c>
       <c r="G72">
-        <v>-10.67793055934768</v>
+        <v>-8.070409410488153</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.75284864567583</v>
       </c>
       <c r="E73">
-        <v>-19.46259087872346</v>
+        <v>-17.11371669568492</v>
       </c>
       <c r="F73">
-        <v>-0.08540234137392838</v>
+        <v>1.092604031533998</v>
       </c>
       <c r="G73">
-        <v>-10.93207101279135</v>
+        <v>-6.700233630473669</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.53562167338886</v>
       </c>
       <c r="E74">
-        <v>-19.6475247002487</v>
+        <v>-15.57747717332283</v>
       </c>
       <c r="F74">
-        <v>-0.0744670632895721</v>
+        <v>1.260621791843822</v>
       </c>
       <c r="G74">
-        <v>-10.5687282246278</v>
+        <v>-6.748244464331464</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.30938585216171</v>
       </c>
       <c r="E75">
-        <v>-20.49344364488152</v>
+        <v>-17.45051742153139</v>
       </c>
       <c r="F75">
-        <v>-0.3723272721512043</v>
+        <v>0.980583907653421</v>
       </c>
       <c r="G75">
-        <v>-10.77776172529378</v>
+        <v>-7.39548838548285</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.07672101062181</v>
       </c>
       <c r="E76">
-        <v>-20.23326017077082</v>
+        <v>-17.13884972642749</v>
       </c>
       <c r="F76">
-        <v>-0.2036666987368082</v>
+        <v>0.4475245137475223</v>
       </c>
       <c r="G76">
-        <v>-10.15384072698693</v>
+        <v>-7.793956650440257</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.842847165501707</v>
       </c>
       <c r="E77">
-        <v>-19.92238495861826</v>
+        <v>-17.14477749890353</v>
       </c>
       <c r="F77">
-        <v>-0.2838352676123416</v>
+        <v>0.7099529636892113</v>
       </c>
       <c r="G77">
-        <v>-10.04927147710899</v>
+        <v>-6.20906429401883</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.620582636408484</v>
       </c>
       <c r="E78">
-        <v>-20.69223459687024</v>
+        <v>-17.71511162932557</v>
       </c>
       <c r="F78">
-        <v>-0.2885784993607715</v>
+        <v>0.2558460953115363</v>
       </c>
       <c r="G78">
-        <v>-10.09860136203368</v>
+        <v>-7.362882886846648</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.412250330616313</v>
       </c>
       <c r="E79">
-        <v>-20.44026124613544</v>
+        <v>-18.4847574862472</v>
       </c>
       <c r="F79">
-        <v>-0.3965553619482843</v>
+        <v>0.5854311189655841</v>
       </c>
       <c r="G79">
-        <v>-9.798044748410103</v>
+        <v>-7.239354738798233</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.222261483432947</v>
       </c>
       <c r="E80">
-        <v>-21.08681412258057</v>
+        <v>-19.63534310516807</v>
       </c>
       <c r="F80">
-        <v>-0.6137673772081622</v>
+        <v>0.4002031974951978</v>
       </c>
       <c r="G80">
-        <v>-9.508263666387743</v>
+        <v>-6.500118490006255</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.060896143001289</v>
       </c>
       <c r="E81">
-        <v>-21.43806520898553</v>
+        <v>-19.37503736225916</v>
       </c>
       <c r="F81">
-        <v>-0.5746220472214688</v>
+        <v>0.5420776825726691</v>
       </c>
       <c r="G81">
-        <v>-9.568326427033378</v>
+        <v>-5.712461254661551</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.927472509265687</v>
       </c>
       <c r="E82">
-        <v>-22.42732846985715</v>
+        <v>-20.50215642887228</v>
       </c>
       <c r="F82">
-        <v>-0.5307575081410266</v>
+        <v>-0.005051531669779137</v>
       </c>
       <c r="G82">
-        <v>-9.206470032236256</v>
+        <v>-5.973301962529608</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.823044149014052</v>
       </c>
       <c r="E83">
-        <v>-23.56877562823054</v>
+        <v>-21.11784775495514</v>
       </c>
       <c r="F83">
-        <v>-0.6273236097549761</v>
+        <v>0.4607949595403704</v>
       </c>
       <c r="G83">
-        <v>-8.834005448137448</v>
+        <v>-6.661859744335963</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.75254683005554</v>
       </c>
       <c r="E84">
-        <v>-23.70257392126117</v>
+        <v>-21.95325158294215</v>
       </c>
       <c r="F84">
-        <v>-0.7136278959830454</v>
+        <v>0.6634061709585043</v>
       </c>
       <c r="G84">
-        <v>-9.166570378073409</v>
+        <v>-5.827458226655409</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.709851315909383</v>
       </c>
       <c r="E85">
-        <v>-25.06760542681527</v>
+        <v>-22.37155578397868</v>
       </c>
       <c r="F85">
-        <v>-0.7289286702801551</v>
+        <v>0.0376218150854374</v>
       </c>
       <c r="G85">
-        <v>-8.822055239217951</v>
+        <v>-6.722519687305417</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.691367356518594</v>
       </c>
       <c r="E86">
-        <v>-25.31101543320155</v>
+        <v>-23.68716352421306</v>
       </c>
       <c r="F86">
-        <v>-0.6812470142076128</v>
+        <v>0.2463049595660916</v>
       </c>
       <c r="G86">
-        <v>-8.499058351349332</v>
+        <v>-5.22230909689014</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.696519258057817</v>
       </c>
       <c r="E87">
-        <v>-26.85470429530626</v>
+        <v>-24.88473206096351</v>
       </c>
       <c r="F87">
-        <v>-0.7021881421503843</v>
+        <v>0.2596118535246629</v>
       </c>
       <c r="G87">
-        <v>-8.09459529460282</v>
+        <v>-4.874345394175705</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.715356906512127</v>
       </c>
       <c r="E88">
-        <v>-27.91527743637667</v>
+        <v>-25.90381079470163</v>
       </c>
       <c r="F88">
-        <v>-0.9593622576561159</v>
+        <v>0.0548808499227651</v>
       </c>
       <c r="G88">
-        <v>-8.181173606670328</v>
+        <v>-5.396765084762696</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.743029758085436</v>
       </c>
       <c r="E89">
-        <v>-29.46632280450684</v>
+        <v>-27.27793094758913</v>
       </c>
       <c r="F89">
-        <v>-0.8263181690924873</v>
+        <v>-0.03549900392707776</v>
       </c>
       <c r="G89">
-        <v>-8.242575105712216</v>
+        <v>-4.8593698989784</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.77846195045462</v>
       </c>
       <c r="E90">
-        <v>-30.66745298606432</v>
+        <v>-29.64268648897256</v>
       </c>
       <c r="F90">
-        <v>-0.868648571742945</v>
+        <v>0.00750237631964737</v>
       </c>
       <c r="G90">
-        <v>-7.953968701008138</v>
+        <v>-4.838130551824114</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.813758596938593</v>
       </c>
       <c r="E91">
-        <v>-32.31834667758962</v>
+        <v>-30.64338414671355</v>
       </c>
       <c r="F91">
-        <v>-1.090545833033057</v>
+        <v>0.09791867833521341</v>
       </c>
       <c r="G91">
-        <v>-7.995561465495659</v>
+        <v>-4.892149302357253</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.847316543445174</v>
       </c>
       <c r="E92">
-        <v>-33.45622313420796</v>
+        <v>-34.24152619001111</v>
       </c>
       <c r="F92">
-        <v>-1.291971650697785</v>
+        <v>-0.3500640698335648</v>
       </c>
       <c r="G92">
-        <v>-7.770735445464067</v>
+        <v>-5.449582908205078</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.880173557910737</v>
       </c>
       <c r="E93">
-        <v>-34.97800097482656</v>
+        <v>-33.48436080745461</v>
       </c>
       <c r="F93">
-        <v>-1.084772940602947</v>
+        <v>-0.3388156688709503</v>
       </c>
       <c r="G93">
-        <v>-7.685289154834567</v>
+        <v>-4.280897100491416</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.906598579572336</v>
       </c>
       <c r="E94">
-        <v>-36.89961363524139</v>
+        <v>-35.61644561856095</v>
       </c>
       <c r="F94">
-        <v>-1.225660011736281</v>
+        <v>-0.6480551607448394</v>
       </c>
       <c r="G94">
-        <v>-8.182390939868881</v>
+        <v>-5.192945445154669</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.926859304244486</v>
       </c>
       <c r="E95">
-        <v>-38.05809917706864</v>
+        <v>-36.98410816751351</v>
       </c>
       <c r="F95">
-        <v>-1.343272443953158</v>
+        <v>-0.1959280904598552</v>
       </c>
       <c r="G95">
-        <v>-8.610232700226438</v>
+        <v>-5.328161304397826</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.94178048993771</v>
       </c>
       <c r="E96">
-        <v>-40.3946468538583</v>
+        <v>-39.26501448417093</v>
       </c>
       <c r="F96">
-        <v>-1.513146575612655</v>
+        <v>-0.9283208459710102</v>
       </c>
       <c r="G96">
-        <v>-8.314220578462692</v>
+        <v>-5.947544373287967</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.947034297562944</v>
       </c>
       <c r="E97">
-        <v>-42.45129408070787</v>
+        <v>-42.25266841802043</v>
       </c>
       <c r="F97">
-        <v>-1.668771131209196</v>
+        <v>-0.7830500545420608</v>
       </c>
       <c r="G97">
-        <v>-8.943286532174755</v>
+        <v>-5.1294144333207</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.940924787004857</v>
       </c>
       <c r="E98">
-        <v>-44.04084959179927</v>
+        <v>-43.19947270659613</v>
       </c>
       <c r="F98">
-        <v>-1.73413014765748</v>
+        <v>-0.2998906846134016</v>
       </c>
       <c r="G98">
-        <v>-8.739512829668559</v>
+        <v>-5.641540931875713</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.922366221528062</v>
       </c>
       <c r="E99">
-        <v>-45.85913832501809</v>
+        <v>-45.12460851978894</v>
       </c>
       <c r="F99">
-        <v>-1.715511761912158</v>
+        <v>-0.5622768878175478</v>
       </c>
       <c r="G99">
-        <v>-9.438183336321122</v>
+        <v>-5.876778267915423</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.886343314328684</v>
       </c>
       <c r="E100">
-        <v>-48.7781304038448</v>
+        <v>-45.8952166774372</v>
       </c>
       <c r="F100">
-        <v>-1.975551200264173</v>
+        <v>-1.490778999002263</v>
       </c>
       <c r="G100">
-        <v>-9.64898213418609</v>
+        <v>-6.737065342478436</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.82961539715604</v>
       </c>
       <c r="E101">
-        <v>-49.61835026393897</v>
+        <v>-49.65342216300987</v>
       </c>
       <c r="F101">
-        <v>-2.061139777056224</v>
+        <v>-1.375650012258979</v>
       </c>
       <c r="G101">
-        <v>-9.79380869137686</v>
+        <v>-6.397294849997936</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.748597105974568</v>
       </c>
       <c r="E102">
-        <v>-52.53372069567804</v>
+        <v>-52.0104374101957</v>
       </c>
       <c r="F102">
-        <v>-2.329862162524383</v>
+        <v>-1.582205909249245</v>
       </c>
       <c r="G102">
-        <v>-9.708851302759717</v>
+        <v>-6.506648120909549</v>
       </c>
     </row>
   </sheetData>
